--- a/data/mining/jasansky/variables_descriptions.xlsx
+++ b/data/mining/jasansky/variables_descriptions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpsich-my.sharepoint.com/personal/alvaro_hahn-menacho_psi_ch/Documents/Severin's work/2_Project/data/mining/jasansky/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpsich-my.sharepoint.com/personal/alvaro_hahn-menacho_psi_ch/Documents/Severin's work/4_Github_Repo/semesterproject/data/mining/jasansky/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="8" documentId="11_2DDDDEC78F79A8D366075C52F37BD2724AC5EBB5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED1CA934-DA93-4C85-96BF-43ADAFC3A9EE}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="3760" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="705" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
